--- a/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260707.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260707.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>18.64%</t>
+          <t>19.44%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>7.37%</t>
+          <t>7.23%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>5.98%</t>
+          <t>5.66%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>5.45%</t>
+          <t>5.26%</t>
         </is>
       </c>
     </row>
@@ -711,22 +711,22 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>7,500,000</t>
+          <t>1,600,000</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.07%</t>
+          <t>4.01%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>4.06%</t>
+          <t>3.93%</t>
         </is>
       </c>
     </row>
@@ -770,29 +770,29 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.69%</t>
+          <t>3.70%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>1,490,000</t>
+          <t>7,064,000</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.64%</t>
+          <t>3.69%</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>3.29%</t>
+          <t>3.21%</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.87%</t>
+          <t>2.86%</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.35%</t>
+          <t>2.47%</t>
         </is>
       </c>
     </row>
@@ -875,12 +875,12 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>5,600,000</t>
+          <t>5,900,000</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.25%</t>
+          <t>2.39%</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.21%</t>
+          <t>2.20%</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.99%</t>
+          <t>1.94%</t>
         </is>
       </c>
     </row>
@@ -946,29 +946,29 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.64%</t>
+          <t>1.67%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>780,000</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.58%</t>
+          <t>1.55%</t>
         </is>
       </c>
     </row>
@@ -990,29 +990,29 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.56%</t>
+          <t>1.52%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>780,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.53%</t>
+          <t>1.50%</t>
         </is>
       </c>
     </row>
@@ -1034,51 +1034,51 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.45%</t>
+          <t>1.38%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>1,560,000</t>
+          <t>480,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.32%</t>
+          <t>1.34%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>480,000</t>
+          <t>1,560,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.31%</t>
+          <t>1.30%</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.12%</t>
+          <t>1.07%</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.06%</t>
+          <t>1.00%</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>0.87%</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>0.83%</t>
+          <t>0.78%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.65%</t>
+          <t>0.63%</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.58%</t>
+          <t>0.55%</t>
         </is>
       </c>
     </row>
@@ -1276,24 +1276,24 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>0.47%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>辛耘</t>
+          <t>力旺</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>900,000</t>
+          <t>269,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -1305,17 +1305,17 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>力旺</t>
+          <t>辛耘</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>269,000</t>
+          <t>900,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1342,24 +1342,24 @@
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>0.44%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>信驊</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>1,000,000</t>
+          <t>49,500</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -1371,22 +1371,22 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>45,000</t>
+          <t>1,000,000</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>0.44%</t>
         </is>
       </c>
     </row>
@@ -1408,51 +1408,51 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>0.34%</t>
+          <t>0.35%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>6415</t>
+          <t>4966</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>矽力*-KY</t>
+          <t>譜瑞-KY</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>900,000</t>
+          <t>800,000</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>0.33%</t>
+          <t>0.32%</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>6415</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>譜瑞-KY</t>
+          <t>矽力*-KY</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>800,000</t>
+          <t>900,000</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.31%</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>0.28%</t>
+          <t>0.29%</t>
         </is>
       </c>
     </row>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>0.19%</t>
+          <t>0.20%</t>
         </is>
       </c>
     </row>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>0.13%</t>
+          <t>0.12%</t>
         </is>
       </c>
     </row>
@@ -1711,7 +1711,7 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>3,811,676,191</t>
+          <t>3,168,214,606</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr"/>
@@ -1747,7 +1747,7 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>1,329,432,015</t>
+          <t>913,522,452</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr"/>
